--- a/data/department_schedules_finals/İnşaat Mühendisliği.xlsx
+++ b/data/department_schedules_finals/İnşaat Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0E0A3EA1-C2E2-4B1F-84AC-00B429DE38D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0125CA14-4C83-45E6-AF12-F93E24920358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="3800" windowWidth="28920" windowHeight="10250" xr2:uid="{91744B99-4786-4948-8AC9-0C0F2BECAA6A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{91744B99-4786-4948-8AC9-0C0F2BECAA6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Filled_Exam_Schedule" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Year:</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>MAT 162</t>
-  </si>
-  <si>
-    <t>JEO 308</t>
   </si>
   <si>
     <t>İNM 104</t>
@@ -706,8 +703,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5046FB1-8390-49B0-AA15-6AA3F4A2AFF1}" name="Table1" displayName="Table1" ref="A1:D35" totalsRowShown="0">
-  <autoFilter ref="A1:D35" xr:uid="{C5046FB1-8390-49B0-AA15-6AA3F4A2AFF1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5046FB1-8390-49B0-AA15-6AA3F4A2AFF1}" name="Table1" displayName="Table1" ref="A1:D34" totalsRowShown="0">
+  <autoFilter ref="A1:D34" xr:uid="{C5046FB1-8390-49B0-AA15-6AA3F4A2AFF1}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{DB671DE9-90D2-4C2F-8769-14A7073BEBFA}" name="Year:"/>
     <tableColumn id="2" xr3:uid="{7494E69D-90F9-44A0-9128-0CAACE54C220}" name="Course ID"/>
@@ -1035,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF810464-3772-4692-AFA3-F8000F5D7FFA}">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.7265625" customWidth="1"/>
@@ -1060,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>8</v>
@@ -1074,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -1088,7 +1085,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
@@ -1116,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1">
         <v>7</v>
@@ -1144,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -1158,7 +1155,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1172,7 +1169,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2">
         <v>5</v>
@@ -1186,7 +1183,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="2">
         <v>3</v>
@@ -1200,7 +1197,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="2">
         <v>3</v>
@@ -1214,7 +1211,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="2">
         <v>5</v>
@@ -1228,7 +1225,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2">
         <v>6</v>
@@ -1242,7 +1239,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2">
         <v>7</v>
@@ -1256,7 +1253,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3">
         <v>7</v>
@@ -1270,7 +1267,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3">
         <v>6</v>
@@ -1284,7 +1281,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3">
         <v>4</v>
@@ -1298,7 +1295,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="3">
         <v>4</v>
@@ -1312,7 +1309,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3">
         <v>8</v>
@@ -1326,7 +1323,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3">
         <v>1</v>
@@ -1340,7 +1337,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="3">
         <v>8</v>
@@ -1354,7 +1351,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="3">
         <v>7</v>
@@ -1368,7 +1365,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C24" s="3">
         <v>5</v>
@@ -1378,17 +1375,17 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
-        <v>3</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="A25" s="4">
+        <v>4</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="3">
-        <v>5</v>
-      </c>
-      <c r="D25" s="3">
-        <v>2</v>
+      <c r="C25" s="4">
+        <v>7</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1399,10 +1396,10 @@
         <v>28</v>
       </c>
       <c r="C26" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D26" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1413,7 +1410,7 @@
         <v>29</v>
       </c>
       <c r="C27" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="4">
         <v>2</v>
@@ -1427,10 +1424,10 @@
         <v>30</v>
       </c>
       <c r="C28" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1441,7 +1438,7 @@
         <v>31</v>
       </c>
       <c r="C29" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D29" s="4">
         <v>1</v>
@@ -1455,7 +1452,7 @@
         <v>32</v>
       </c>
       <c r="C30" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D30" s="4">
         <v>1</v>
@@ -1469,7 +1466,7 @@
         <v>33</v>
       </c>
       <c r="C31" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D31" s="4">
         <v>1</v>
@@ -1483,7 +1480,7 @@
         <v>34</v>
       </c>
       <c r="C32" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D32" s="4">
         <v>1</v>
@@ -1497,7 +1494,7 @@
         <v>35</v>
       </c>
       <c r="C33" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" s="4">
         <v>1</v>
@@ -1511,23 +1508,9 @@
         <v>36</v>
       </c>
       <c r="C34" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D34" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="4">
-        <v>4</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="4">
-        <v>8</v>
-      </c>
-      <c r="D35" s="4">
         <v>1</v>
       </c>
     </row>

--- a/data/department_schedules_finals/İnşaat Mühendisliği.xlsx
+++ b/data/department_schedules_finals/İnşaat Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\modified\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_finals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323EAFD4-1814-4EB7-85AF-01CE29E0645B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{323EAFD4-1814-4EB7-85AF-01CE29E0645B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{352D1303-D195-4317-A50E-5A98E799542D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="80">
   <si>
     <t>Year:</t>
   </si>
@@ -236,6 +236,30 @@
   </si>
   <si>
     <t>Rooms Used</t>
+  </si>
+  <si>
+    <t>C203,C209,C213</t>
+  </si>
+  <si>
+    <t>C203,C209,C210,C213</t>
+  </si>
+  <si>
+    <t>C209,C213</t>
+  </si>
+  <si>
+    <t>C209</t>
+  </si>
+  <si>
+    <t>C213</t>
+  </si>
+  <si>
+    <t>C203</t>
+  </si>
+  <si>
+    <t>YLAB 2,YLAB 3</t>
+  </si>
+  <si>
+    <t>YLAB 2</t>
   </si>
 </sst>
 </file>
@@ -357,7 +381,21 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -388,20 +426,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -416,15 +440,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F9B0E3CD-62B9-4A40-9983-B73A52C93363}" name="Table1" displayName="Table1" ref="A1:F34" totalsRowShown="0" headerRowDxfId="7" dataDxfId="0" headerRowBorderDxfId="8" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F9B0E3CD-62B9-4A40-9983-B73A52C93363}" name="Table1" displayName="Table1" ref="A1:F34" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
   <autoFilter ref="A1:F34" xr:uid="{F9B0E3CD-62B9-4A40-9983-B73A52C93363}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F34">
+    <sortCondition ref="C1:C34"/>
+  </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{4217D035-DA80-4815-84AC-12E9DBABE214}" name="Year:" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{FB87D92A-DCBD-4F73-88EC-BA7CD9702E79}" name="Course ID" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{1AC2BE0A-2EEA-45B8-A74B-A82C5FB0B97A}" name="Date" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{DD3D160B-38E0-473E-ADCD-4E0E92D95048}" name="Rooms" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{EEB78D15-5F1B-4C70-A039-5F870979D854}" name="Course Name" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{A12AD2B5-0CF4-4181-ADA5-046FC0F6D1C2}" name="Rooms Used" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{4217D035-DA80-4815-84AC-12E9DBABE214}" name="Year:" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{FB87D92A-DCBD-4F73-88EC-BA7CD9702E79}" name="Course ID" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{1AC2BE0A-2EEA-45B8-A74B-A82C5FB0B97A}" name="Date" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{DD3D160B-38E0-473E-ADCD-4E0E92D95048}" name="Rooms" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{EEB78D15-5F1B-4C70-A039-5F870979D854}" name="Course Name" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{A12AD2B5-0CF4-4181-ADA5-046FC0F6D1C2}" name="Rooms Used" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -718,14 +745,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="31.6328125" customWidth="1"/>
-    <col min="6" max="6" width="33.1796875" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="31.59765625" customWidth="1"/>
+    <col min="6" max="6" width="33.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -745,97 +772,107 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2">
-        <v>4</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F6" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -851,63 +888,71 @@
       <c r="E7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
-        <v>3</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
-        <v>2</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>2</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="3">
-        <v>5</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F7" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="5">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="5">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -923,9 +968,11 @@
       <c r="E11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F11" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -941,387 +988,431 @@
       <c r="E12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
-        <v>2</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="5">
+        <v>4</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" s="5">
+        <v>4</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="4">
+        <v>3</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="4">
+        <v>4</v>
+      </c>
+      <c r="D15" s="4">
+        <v>3</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="4">
+        <v>3</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="4">
+        <v>4</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="2">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2">
+        <v>5</v>
+      </c>
+      <c r="D17" s="2">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="3">
+        <v>2</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="3">
+        <v>5</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="3">
+        <v>2</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C19" s="3">
         <v>5</v>
       </c>
-      <c r="D13" s="3">
-        <v>3</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="D19" s="3">
+        <v>3</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
-        <v>2</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="F19" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="4">
+        <v>3</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="4">
+        <v>5</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="3">
+        <v>2</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C21" s="3">
         <v>6</v>
       </c>
-      <c r="D14" s="3">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D21" s="3">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
-        <v>2</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="F21" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="4">
+        <v>3</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="4">
+        <v>6</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="2">
+        <v>1</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2">
+        <v>7</v>
+      </c>
+      <c r="D23" s="2">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="3">
+        <v>2</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C24" s="3">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="4">
+        <v>3</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="4">
         <v>7</v>
       </c>
-      <c r="D15" s="3">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
-        <v>3</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="D25" s="4">
+        <v>4</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" s="4">
+        <v>3</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="4">
         <v>7</v>
       </c>
-      <c r="D16" s="4">
-        <v>4</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" s="5">
+        <v>4</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="5">
+        <v>7</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" s="5">
+        <v>4</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="5">
+        <v>7</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" s="2">
+        <v>1</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" s="2">
+        <v>1</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" s="4">
+        <v>3</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="4">
+        <v>8</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" s="4">
+        <v>3</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="4">
+        <v>8</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" s="5">
+        <v>4</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="5">
         <v>6</v>
       </c>
-      <c r="D17" s="4">
-        <v>2</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
-        <v>3</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="4">
-        <v>4</v>
-      </c>
-      <c r="D18" s="4">
-        <v>3</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
-        <v>3</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="4">
-        <v>4</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
-        <v>3</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="4">
-        <v>8</v>
-      </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
-        <v>3</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="4">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4">
-        <v>2</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
-        <v>3</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="4">
-        <v>8</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
-        <v>3</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="4">
-        <v>7</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="4">
-        <v>3</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="4">
-        <v>5</v>
-      </c>
-      <c r="D24" s="4">
-        <v>2</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="5">
-        <v>4</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="5">
-        <v>7</v>
-      </c>
-      <c r="D25" s="5">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="5">
-        <v>4</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="5">
-        <v>2</v>
-      </c>
-      <c r="D26" s="5">
-        <v>2</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="5"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="5">
-        <v>4</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="5">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5">
-        <v>2</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="5">
-        <v>4</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="5">
-        <v>2</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="5">
-        <v>4</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="5">
-        <v>7</v>
-      </c>
-      <c r="D29" s="5">
-        <v>1</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="5">
-        <v>4</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="5">
-        <v>3</v>
-      </c>
-      <c r="D30" s="5">
-        <v>1</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="5">
-        <v>4</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="5">
-        <v>8</v>
-      </c>
-      <c r="D31" s="5">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5" t="s">
+      <c r="D33" s="5">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F31" s="5"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="5">
-        <v>4</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="5">
-        <v>2</v>
-      </c>
-      <c r="D32" s="5">
-        <v>1</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="5">
-        <v>4</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" s="5">
-        <v>3</v>
-      </c>
-      <c r="D33" s="5">
-        <v>1</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F33" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" s="5">
         <v>4</v>
       </c>
@@ -1329,7 +1420,7 @@
         <v>37</v>
       </c>
       <c r="C34" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D34" s="5">
         <v>1</v>
@@ -1337,7 +1428,9 @@
       <c r="E34" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F34" s="5"/>
+      <c r="F34" s="5" t="s">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/department_schedules_finals/İnşaat Mühendisliği.xlsx
+++ b/data/department_schedules_finals/İnşaat Mühendisliği.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_finals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{323EAFD4-1814-4EB7-85AF-01CE29E0645B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{352D1303-D195-4317-A50E-5A98E799542D}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{323EAFD4-1814-4EB7-85AF-01CE29E0645B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF690A10-F071-46BA-A71A-A6D0C6AF11BB}"/>
   <bookViews>
     <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -439,11 +439,15 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F9B0E3CD-62B9-4A40-9983-B73A52C93363}" name="Table1" displayName="Table1" ref="A1:F34" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
   <autoFilter ref="A1:F34" xr:uid="{F9B0E3CD-62B9-4A40-9983-B73A52C93363}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F34">
-    <sortCondition ref="C1:C34"/>
+    <sortCondition ref="B1:B34"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{4217D035-DA80-4815-84AC-12E9DBABE214}" name="Year:" dataDxfId="5"/>
@@ -793,63 +797,63 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <v>2</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>74</v>
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -857,99 +861,99 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="2">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="5">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="5">
-        <v>2</v>
-      </c>
-      <c r="D8" s="5">
-        <v>2</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>74</v>
+      <c r="A8" s="3">
+        <v>2</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3">
+        <v>6</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="5">
-        <v>4</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>75</v>
+      <c r="A9" s="3">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="5">
-        <v>4</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>76</v>
+      <c r="A10" s="3">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -957,16 +961,16 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>72</v>
@@ -993,43 +997,43 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="5">
-        <v>4</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="5">
-        <v>3</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>77</v>
+      <c r="A13" s="3">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="3">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="5">
-        <v>4</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="5">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>76</v>
+      <c r="A14" s="4">
+        <v>3</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="4">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
@@ -1057,79 +1061,79 @@
         <v>3</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C16" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D16" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" s="2">
-        <v>1</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2">
-        <v>4</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>73</v>
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="4">
+        <v>8</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" s="3">
-        <v>2</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="3">
-        <v>5</v>
-      </c>
-      <c r="D18" s="3">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>72</v>
+      <c r="A18" s="4">
+        <v>3</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" s="3">
-        <v>2</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="3">
-        <v>5</v>
-      </c>
-      <c r="D19" s="3">
-        <v>3</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>72</v>
+      <c r="A19" s="4">
+        <v>3</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="4">
+        <v>6</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
@@ -1137,39 +1141,39 @@
         <v>3</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="4">
+        <v>4</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="4">
+        <v>3</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C21" s="4">
         <v>5</v>
       </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="D21" s="4">
+        <v>2</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" s="3">
-        <v>2</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="3">
-        <v>6</v>
-      </c>
-      <c r="D21" s="3">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.45">
@@ -1177,98 +1181,98 @@
         <v>3</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4">
+        <v>7</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="5">
+        <v>4</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="5">
+        <v>4</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="5">
+        <v>7</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="5">
+        <v>4</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="5">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" s="5">
+        <v>4</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="5">
         <v>6</v>
       </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" s="2">
-        <v>1</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="2">
-        <v>7</v>
-      </c>
-      <c r="D23" s="2">
-        <v>3</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="3">
-        <v>2</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="3">
-        <v>8</v>
-      </c>
-      <c r="D24" s="3">
-        <v>4</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="4">
-        <v>3</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="4">
-        <v>7</v>
-      </c>
-      <c r="D25" s="4">
-        <v>4</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A26" s="4">
-        <v>3</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="4">
-        <v>7</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="4" t="s">
+      <c r="D26" s="5">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1277,19 +1281,19 @@
         <v>4</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C27" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D27" s="5">
         <v>1</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.45">
@@ -1297,139 +1301,139 @@
         <v>4</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C28" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A29" s="2">
-        <v>1</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="A29" s="5">
+        <v>4</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="5">
+        <v>6</v>
+      </c>
+      <c r="D29" s="5">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" s="5">
+        <v>4</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="5">
+        <v>7</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" s="5">
+        <v>4</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="5">
+        <v>3</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" s="5">
+        <v>4</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="5">
+        <v>2</v>
+      </c>
+      <c r="D32" s="5">
+        <v>2</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" s="2">
+        <v>1</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="2">
-        <v>1</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A30" s="2">
-        <v>1</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="C33" s="2">
         <v>8</v>
       </c>
-      <c r="C30" s="2">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A31" s="4">
-        <v>3</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="4">
-        <v>8</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A32" s="4">
-        <v>3</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="4">
-        <v>8</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A33" s="5">
-        <v>4</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="5">
-        <v>6</v>
-      </c>
-      <c r="D33" s="5">
-        <v>1</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A34" s="5">
-        <v>4</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="5">
-        <v>6</v>
-      </c>
-      <c r="D34" s="5">
-        <v>1</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>76</v>
+      <c r="A34" s="2">
+        <v>1</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2</v>
+      </c>
+      <c r="D34" s="2">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
